--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,60 +467,125 @@
           <t>Expenditure</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Receipt_Image</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46197.51343832938</v>
+        <v>46198.65596261882</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C2" t="n">
-        <v>3442</v>
+        <v>3000</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pesticides</t>
-        </is>
-      </c>
+          <t>tractor fuel</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46197.50397167824</v>
+        <v>46198.6511860301</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>tractor driver</t>
-        </is>
-      </c>
+          <t>2 women labor</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46196.76465297454</v>
+        <v>46198.49051479167</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>3425</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
+          <t>pesticides</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46197.51343833334</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3442</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pesticides</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46197.50397167824</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>tractor driver</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46196.76465297454</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>tractor driver</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -533,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,23 +620,34 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B2" t="n">
-        <v>4442</v>
+        <v>7025</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4442</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>46196</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>1000</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -433,8 +433,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -454,20 +461,10 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Expenditure</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Expenditure</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Receipt_Image</t>
         </is>
@@ -475,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46198.65596261882</v>
+        <v>46198.65596261574</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>46198</v>
@@ -483,14 +480,12 @@
       <c r="C2" t="n">
         <v>3000</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>tractor fuel</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>tractor fuel</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -502,14 +497,12 @@
       <c r="C3" t="n">
         <v>600</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2 women labor</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2 women labor</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -521,14 +514,12 @@
       <c r="C4" t="n">
         <v>3425</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pesticides</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>pesticides</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -540,14 +531,12 @@
       <c r="C5" t="n">
         <v>3442</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pesticides</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>pesticides</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -559,14 +548,12 @@
       <c r="C6" t="n">
         <v>1000</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>tractor driver</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>tractor driver</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -578,14 +565,12 @@
       <c r="C7" t="n">
         <v>1000</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tractor driver</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>tractor driver</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -600,6 +585,11 @@
   </sheetPr>
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
